--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104719_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104719_W29.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.8437</v>
+        <v>8.3331</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6342</v>
+        <v>6.2644</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2095</v>
+        <v>2.0687</v>
       </c>
       <c r="G2" t="n">
-        <v>7.4781</v>
+        <v>7.4619</v>
       </c>
       <c r="H2" t="n">
-        <v>2.5396</v>
+        <v>2.5287</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9384</v>
+        <v>4.9332</v>
       </c>
       <c r="J2" t="n">
-        <v>7.5812</v>
+        <v>7.5573</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2992</v>
+        <v>2.285</v>
       </c>
       <c r="L2" t="n">
-        <v>5.2819</v>
+        <v>5.2723</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.1031</v>
+        <v>-0.0954</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2404</v>
+        <v>0.2437</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3435</v>
+        <v>-0.3391</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5016</v>
+        <v>1.0094</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2207</v>
+        <v>0.4387</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.5707</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="W2" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9847</v>
+        <v>5.5539</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7673</v>
+        <v>1.8236</v>
       </c>
       <c r="F3" t="n">
-        <v>4.2173</v>
+        <v>3.7304</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1052</v>
+        <v>2.1016</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3562</v>
+        <v>1.3505</v>
       </c>
       <c r="I3" t="n">
-        <v>0.749</v>
+        <v>0.7511</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0025</v>
+        <v>0.9945000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.928</v>
+        <v>0.9201</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M3" t="n">
-        <v>1.1026</v>
+        <v>1.1071</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4282</v>
+        <v>0.4305</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6744</v>
+        <v>0.6766</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9476</v>
+        <v>0.5206</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4858</v>
+        <v>-0.4182</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4335</v>
+        <v>0.9388</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0231</v>
+        <v>2.0212</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X3" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2245</v>
+        <v>4.5391</v>
       </c>
       <c r="E4" t="n">
-        <v>3.015</v>
+        <v>2.4704</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2095</v>
+        <v>2.0687</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5082</v>
+        <v>0.5007</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4915</v>
+        <v>1.4805</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9833</v>
+        <v>-0.9798</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6113</v>
+        <v>0.5961</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2511</v>
+        <v>1.2368</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6398</v>
+        <v>-0.6407</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1031</v>
+        <v>-0.0954</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2404</v>
+        <v>0.2437</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3435</v>
+        <v>-0.3391</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0794</v>
+        <v>1.4042</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3571</v>
+        <v>0.8335</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.5707</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.326</v>
+        <v>3.5855</v>
       </c>
       <c r="E5" t="n">
-        <v>4.2005</v>
+        <v>3.3522</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1255</v>
+        <v>0.2333</v>
       </c>
       <c r="G5" t="n">
-        <v>1.758</v>
+        <v>1.7495</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4037</v>
+        <v>3.3905</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6457</v>
+        <v>-1.641</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8922</v>
+        <v>2.8766</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8177</v>
+        <v>2.8021</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1271</v>
       </c>
       <c r="N5" t="n">
-        <v>0.586</v>
+        <v>0.5884</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.7203</v>
+        <v>-1.7155</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>2.7952</v>
+        <v>2.0637</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2848</v>
+        <v>1.456</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5104</v>
+        <v>0.6077</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4556</v>
+        <v>1.6928</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6078</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8478</v>
+        <v>1.1418</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1576</v>
+        <v>-0.1529</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9835</v>
+        <v>0.9848</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1411</v>
+        <v>-1.1377</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1033</v>
+        <v>0.1005</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7431</v>
+        <v>0.7412</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6398</v>
+        <v>-0.6407</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2609</v>
+        <v>-0.2533</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2404</v>
+        <v>0.2437</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5013</v>
+        <v>-0.497</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5219</v>
+        <v>0.7561</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5492</v>
+        <v>0.4991</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0273</v>
+        <v>0.257</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. NUNEZ</t>
+          <t>D. BRIZUELA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0159</v>
+        <v>0.8073</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3993</v>
+        <v>0.3976</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4152</v>
+        <v>0.4096</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.2368</v>
+        <v>0.4438</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5266999999999999</v>
+        <v>2.5278</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.7635</v>
+        <v>-2.084</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5175999999999999</v>
+        <v>0.2538</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2713</v>
+        <v>1.7959</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7889</v>
+        <v>-1.542</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7192</v>
+        <v>0.19</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2554</v>
+        <v>0.7319</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9746</v>
+        <v>-0.5419</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4117</v>
+        <v>0.77</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5492</v>
+        <v>0.1438</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8625</v>
+        <v>0.6262</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3862</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. NORRIS</t>
+          <t>M. CALE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1328</v>
+        <v>0.1793</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.8126</v>
+        <v>-1.243</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6798</v>
+        <v>1.4224</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7658</v>
+        <v>1.6822</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7867</v>
+        <v>0.8297</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5524</v>
+        <v>0.8525</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5199</v>
+        <v>0.3158</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0579</v>
+        <v>0.2413</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5778</v>
+        <v>0.0745</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2459</v>
+        <v>1.3664</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7288</v>
+        <v>0.5884</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9746</v>
+        <v>0.778</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3631</v>
+        <v>0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S8" t="n">
-        <v>2.1335</v>
+        <v>0.4484</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4798</v>
+        <v>-0.4207</v>
       </c>
       <c r="U8" t="n">
-        <v>1.6537</v>
+        <v>0.8691</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8637</v>
+        <v>-2.1789</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7724</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0913</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BRIZUELA</t>
+          <t>J. PARRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1362</v>
+        <v>0.009900000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0653</v>
+        <v>1.6879</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0709</v>
+        <v>-1.678</v>
       </c>
       <c r="G9" t="n">
-        <v>0.447</v>
+        <v>-2.92</v>
       </c>
       <c r="H9" t="n">
-        <v>2.5321</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0851</v>
+        <v>-2.9982</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2628</v>
+        <v>-0.7599</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8033</v>
+        <v>-0.0075</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5405</v>
+        <v>-0.7524</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1842</v>
+        <v>-2.1601</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7288</v>
+        <v>0.0857</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5446</v>
+        <v>-2.2458</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6816</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1735</v>
+        <v>1.634</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3281</v>
+        <v>1.2005</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1546</v>
+        <v>0.4335</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0913</v>
+        <v>0.1578</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. CALE</t>
+          <t>J. NUNEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2691</v>
+        <v>-0.0134</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4251</v>
+        <v>-0.4124</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1561</v>
+        <v>0.399</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6775</v>
+        <v>-1.2373</v>
       </c>
       <c r="H10" t="n">
-        <v>0.828</v>
+        <v>0.5232</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8495</v>
+        <v>-1.7604</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3165</v>
+        <v>-0.5246</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2419</v>
+        <v>0.2651</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0746</v>
+        <v>-0.7896</v>
       </c>
       <c r="M10" t="n">
-        <v>1.361</v>
+        <v>-0.7127</v>
       </c>
       <c r="N10" t="n">
-        <v>0.586</v>
+        <v>0.2581</v>
       </c>
       <c r="O10" t="n">
-        <v>0.7749</v>
+        <v>-0.9708</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>0.008800000000000001</v>
+        <v>1.3832</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6057</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6145</v>
+        <v>0.8353</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.1825</v>
+        <v>-0.387</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1825</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. PARRA</t>
+          <t>M. NORRIS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3785</v>
+        <v>-0.5291</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3457</v>
+        <v>-1.8201</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7242</v>
+        <v>1.291</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.919</v>
+        <v>-1.7632</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0834</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.0025</v>
+        <v>-2.5501</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7508</v>
+        <v>-1.5243</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0008</v>
+        <v>0.055</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7516</v>
+        <v>-1.5793</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1682</v>
+        <v>-0.2389</v>
       </c>
       <c r="N11" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.7319</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.2508</v>
+        <v>-0.9708</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1359</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1359</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>1.2451</v>
+        <v>1.7317</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8458</v>
+        <v>0.4782</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3993</v>
+        <v>1.2536</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1594</v>
+        <v>-1.8634</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2507</v>
+        <v>-0.7739</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. KEITA</t>
+          <t>D. GONZALEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4226</v>
+        <v>-1.3874</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3541</v>
+        <v>-1.1561</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7767</v>
+        <v>-0.2312</v>
       </c>
       <c r="G12" t="n">
-        <v>0.555</v>
+        <v>-0.406</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1428</v>
+        <v>0.1808</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3307</v>
+        <v>0.0517</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3307</v>
+        <v>0.0517</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7756999999999999</v>
+        <v>-0.4578</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1878</v>
+        <v>0.129</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.137</v>
+        <v>-0.0708</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>-0.0697</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.137</v>
+        <v>-0.0011</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9318</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1594</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0913</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. GONZALEZ</t>
+          <t>S. KEITA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.4818</v>
+        <v>-1.3943</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.1535</v>
+        <v>0.3468</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3283</v>
+        <v>-1.7411</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.4083</v>
+        <v>0.5536</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1796</v>
+        <v>1.1404</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0518</v>
+        <v>1.3272</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0518</v>
+        <v>1.3272</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4601</v>
+        <v>-0.7736</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1277</v>
+        <v>-0.1868</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1647</v>
+        <v>-0.1057</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0694</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0953</v>
+        <v>-0.1057</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>21.0294</v>
+        <v>21.3767</v>
       </c>
       <c r="E14" t="n">
-        <v>12.0688</v>
+        <v>12.2622</v>
       </c>
       <c r="F14" t="n">
-        <v>8.960600000000001</v>
+        <v>9.114600000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>8.041500000000001</v>
+        <v>8.0139</v>
       </c>
       <c r="H14" t="n">
-        <v>15.8538</v>
+        <v>15.802</v>
       </c>
       <c r="I14" t="n">
-        <v>-7.8123</v>
+        <v>-7.788</v>
       </c>
       <c r="J14" t="n">
-        <v>11.364</v>
+        <v>11.2647</v>
       </c>
       <c r="K14" t="n">
-        <v>11.7968</v>
+        <v>11.7139</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4327000000000001</v>
+        <v>-0.4489000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.3226</v>
+        <v>-3.2508</v>
       </c>
       <c r="N14" t="n">
-        <v>4.056900000000001</v>
+        <v>4.088200000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.379499999999998</v>
+        <v>-7.339</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2719</v>
+        <v>2.276400000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.2232</v>
+        <v>-10.2437</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4951</v>
+        <v>12.5197</v>
       </c>
       <c r="S14" t="n">
-        <v>11.1696</v>
+        <v>11.5448</v>
       </c>
       <c r="T14" t="n">
-        <v>4.3562</v>
+        <v>4.6891</v>
       </c>
       <c r="U14" t="n">
-        <v>6.813499999999999</v>
+        <v>6.8558</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4536000000000004</v>
+        <v>-0.4584000000000004</v>
       </c>
       <c r="W14" t="n">
-        <v>6.5722</v>
+        <v>6.5517</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.026</v>
+        <v>-7.0103</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3183</v>
+        <v>1.6193</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1972</v>
+        <v>1.4178</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1211</v>
+        <v>0.2015</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5877</v>
+        <v>3.5904</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.3194</v>
+        <v>-1.3133</v>
       </c>
       <c r="I15" t="n">
-        <v>4.9072</v>
+        <v>4.9037</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2161</v>
+        <v>4.2083</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0406</v>
+        <v>0.0377</v>
       </c>
       <c r="L15" t="n">
-        <v>4.1755</v>
+        <v>4.1705</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6284</v>
+        <v>-0.6179</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.36</v>
+        <v>-1.351</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7317</v>
+        <v>0.7331</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.656</v>
+        <v>-1.3565</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1105</v>
+        <v>-0.8784</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5455</v>
+        <v>-0.4782</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="16">
@@ -1657,49 +1657,49 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1629</v>
+        <v>1.162</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1085</v>
+        <v>1.1067</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0544</v>
+        <v>0.0553</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1555</v>
+        <v>-0.1551</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1555</v>
+        <v>-0.1551</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1728</v>
+        <v>-0.1724</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1711,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MITEO</t>
+          <t>K. ROBERTSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1026</v>
+        <v>0.0999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4115</v>
+        <v>1.4065</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3089</v>
+        <v>-1.3067</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6576</v>
+        <v>2.2842</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5831</v>
+        <v>-2.6028</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0746</v>
+        <v>4.887</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8754999999999999</v>
+        <v>3.5322</v>
       </c>
       <c r="K17" t="n">
-        <v>0.801</v>
+        <v>-1.5243</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0746</v>
+        <v>5.0565</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2179</v>
+        <v>-1.248</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2179</v>
+        <v>-1.0784</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.1695</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6816</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1359</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4544</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2859</v>
+        <v>-1.5714</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5807</v>
+        <v>-0.7599</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2947</v>
+        <v>-0.8115</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0913</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2507</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>Z. SAMAR</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0161</v>
+        <v>-0.0106</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9296</v>
+        <v>1.1029</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9136</v>
+        <v>-1.1135</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.4371</v>
+        <v>0.7317</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7687</v>
+        <v>-0.4971</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6684</v>
+        <v>1.2288</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.066</v>
+        <v>1.2633</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0579</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1238</v>
+        <v>1.2288</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3711</v>
+        <v>-0.5315</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8265</v>
+        <v>-0.5315</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5446</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9087</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9087</v>
+        <v>0.4553</v>
       </c>
       <c r="S18" t="n">
-        <v>0.385</v>
+        <v>-0.1081</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7449</v>
+        <v>-0.1604</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.36</v>
+        <v>0.0523</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1594</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2507</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Z. SAMAR</t>
+          <t>M. MITEO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1623</v>
+        <v>-0.3426</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9872</v>
+        <v>0.9287</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1495</v>
+        <v>-1.2712</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.6549</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4989</v>
+        <v>0.5805</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2303</v>
+        <v>0.0745</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2648</v>
+        <v>0.8706</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0346</v>
+        <v>0.7961</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2303</v>
+        <v>0.0745</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5335</v>
+        <v>-0.2157</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5335</v>
+        <v>-0.2157</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4544</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2568</v>
+        <v>-0.1568</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2776</v>
+        <v>0.1067</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0208</v>
+        <v>-0.2636</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0913</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0913</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="20">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9328</v>
+        <v>-0.4715</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1925</v>
+        <v>0.416</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1252</v>
+        <v>-0.8875</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2424</v>
+        <v>-1.2368</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7664</v>
+        <v>-0.7617</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.476</v>
+        <v>-0.4751</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6019</v>
+        <v>-0.6057</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0752</v>
+        <v>0.0722</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6771</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6405</v>
+        <v>-0.631</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8416</v>
+        <v>-0.8339</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2011</v>
+        <v>0.2028</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3719</v>
+        <v>-0.9176</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3881</v>
+        <v>-1.1572</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0162</v>
+        <v>0.2396</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. ROBERTSON</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0413</v>
+        <v>-0.6486</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0707</v>
+        <v>1.0889</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.112</v>
+        <v>-1.7375</v>
       </c>
       <c r="G21" t="n">
-        <v>2.283</v>
+        <v>-1.4334</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6095</v>
+        <v>-0.7645</v>
       </c>
       <c r="I21" t="n">
-        <v>4.8925</v>
+        <v>-0.669</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5443</v>
+        <v>-0.0721</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5199</v>
+        <v>0.055</v>
       </c>
       <c r="L21" t="n">
-        <v>5.0643</v>
+        <v>-0.127</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2613</v>
+        <v>-1.3613</v>
       </c>
       <c r="N21" t="n">
+        <v>-0.8194</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-0.5419</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.9105</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.9105</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.2834</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.0863</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.1972</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.1578</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.2472</v>
+      </c>
+      <c r="X21" t="n">
         <v>-1.0895</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-0.1718</v>
-      </c>
-      <c r="P21" t="n">
-        <v>-0.4544</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-1.3631</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.9087</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-2.7105</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-1.1105</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-0.1594</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.1594</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5847</v>
+        <v>-1.531</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.7959</v>
+        <v>-1.6842</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2113</v>
+        <v>0.1532</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7037</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0917</v>
+        <v>-2.0908</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3881</v>
+        <v>1.3867</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.313</v>
+        <v>-0.316</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5432</v>
+        <v>-1.5448</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2303</v>
+        <v>1.2288</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3907</v>
+        <v>-0.3881</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5485</v>
+        <v>-0.546</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1578</v>
+        <v>0.1579</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1994</v>
+        <v>-0.144</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.347</v>
+        <v>-0.2301</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1476</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5781</v>
+        <v>-3.1767</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8562</v>
+        <v>-3.2258</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2781</v>
+        <v>0.0491</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0159</v>
+        <v>-2.0142</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.3675</v>
+        <v>-1.3645</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6484</v>
+        <v>-0.6497000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8909</v>
+        <v>-1.899</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1953</v>
+        <v>-0.2003</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.6956</v>
+        <v>-1.6987</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.125</v>
+        <v>-0.1152</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1722</v>
+        <v>-1.1642</v>
       </c>
       <c r="O23" t="n">
-        <v>1.0472</v>
+        <v>1.049</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2202</v>
+        <v>-0.8258</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7381</v>
+        <v>-1.0992</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5178</v>
+        <v>0.2733</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0557</v>
+        <v>-4.534</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6791</v>
+        <v>-4.9331</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3766</v>
+        <v>0.3991</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.1755</v>
+        <v>-4.1674</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2323</v>
+        <v>-1.2219</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.9432</v>
+        <v>-2.9454</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.7414</v>
+        <v>-2.747</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3456</v>
+        <v>0.3447</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.087</v>
+        <v>-3.0918</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4341</v>
+        <v>-1.4203</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.5779</v>
+        <v>-1.5667</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1438</v>
+        <v>0.1463</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.6079</v>
+        <v>-1.0919</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5298</v>
+        <v>-0.7716</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0781</v>
+        <v>-0.3202</v>
       </c>
       <c r="V24" t="n">
-        <v>1.8637</v>
+        <v>1.8634</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.83</v>
+        <v>-4.7248</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.4111</v>
+        <v>-2.9533</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4189</v>
+        <v>-1.7715</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.9071</v>
+        <v>-2.9036</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.2008</v>
+        <v>-2.1923</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7064</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.7292</v>
+        <v>-0.7369</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6679</v>
+        <v>-0.669</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.0613</v>
+        <v>-0.0679</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.1779</v>
+        <v>-2.1667</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.5328</v>
+        <v>-1.5233</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.6451</v>
+        <v>-0.6433</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.6722</v>
+        <v>-0.574</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.3187</v>
+        <v>-0.8506</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3535</v>
+        <v>0.2766</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="26">
@@ -2437,64 +2437,64 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-6.4445</v>
+        <v>-5.3112</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.1155</v>
+        <v>-3.7857</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.3289</v>
+        <v>-1.5255</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.6639</v>
+        <v>-2.6608</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.4262</v>
+        <v>-3.4185</v>
       </c>
       <c r="I26" t="n">
-        <v>0.7623</v>
+        <v>0.7577</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2531</v>
+        <v>-0.264</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.5026</v>
+        <v>-1.5071</v>
       </c>
       <c r="L26" t="n">
-        <v>1.2496</v>
+        <v>1.243</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.4109</v>
+        <v>-2.3968</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.9235</v>
+        <v>-1.9114</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.4873</v>
+        <v>-0.4854</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.7262</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.635</v>
+        <v>-3.6421</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.1456</v>
+        <v>-1.0083</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.3187</v>
+        <v>-0.969</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8268</v>
+        <v>-0.0392</v>
       </c>
       <c r="V26" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W26" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-21.0295</v>
+        <v>-17.8698</v>
       </c>
       <c r="E27" t="n">
-        <v>-8.960599999999999</v>
+        <v>-9.114599999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-12.0687</v>
+        <v>-8.755199999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>-8.041399999999999</v>
+        <v>-8.014200000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>-15.8538</v>
+        <v>-15.802</v>
       </c>
       <c r="I27" t="n">
-        <v>7.812599999999997</v>
+        <v>7.788</v>
       </c>
       <c r="J27" t="n">
-        <v>3.322499999999998</v>
+        <v>3.250900000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.0567</v>
+        <v>-4.0881</v>
       </c>
       <c r="L27" t="n">
-        <v>7.379799999999999</v>
+        <v>7.3388</v>
       </c>
       <c r="M27" t="n">
-        <v>-11.3641</v>
+        <v>-11.2649</v>
       </c>
       <c r="N27" t="n">
-        <v>-11.7967</v>
+        <v>-11.7139</v>
       </c>
       <c r="O27" t="n">
-        <v>0.4327999999999999</v>
+        <v>0.4490000000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.272</v>
+        <v>-2.2764</v>
       </c>
       <c r="Q27" t="n">
-        <v>-12.4952</v>
+        <v>-12.5198</v>
       </c>
       <c r="R27" t="n">
-        <v>10.2232</v>
+        <v>10.2435</v>
       </c>
       <c r="S27" t="n">
-        <v>-11.1696</v>
+        <v>-8.037799999999999</v>
       </c>
       <c r="T27" t="n">
-        <v>-6.813399999999999</v>
+        <v>-6.856000000000001</v>
       </c>
       <c r="U27" t="n">
-        <v>-4.3562</v>
+        <v>-1.1821</v>
       </c>
       <c r="V27" t="n">
-        <v>0.4536</v>
+        <v>0.4583999999999997</v>
       </c>
       <c r="W27" t="n">
-        <v>7.026</v>
+        <v>7.0102</v>
       </c>
       <c r="X27" t="n">
-        <v>-6.572399999999999</v>
+        <v>-6.5517</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104719_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104719_W29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.0103</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104719_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-6.5517</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
